--- a/figures/figure5/iPGC-protein-longevity/data/iPGC intensities.xlsx
+++ b/figures/figure5/iPGC-protein-longevity/data/iPGC intensities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/staff/Moritz/Quantification/iPGC intensities over time/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/julian/Library/Mobile Documents/com~apple~CloudDocs/Documents/General Science/Programming/py/general_analysis/20260528_protein_longevity_replotting/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98DC5E16-622B-BD48-8991-AF3CEF9FC0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CCEDB2-FB79-564D-82A8-705BC6CA195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10760" yWindow="3460" windowWidth="26400" windowHeight="16280" activeTab="6" xr2:uid="{7EBB69BE-C1A5-8748-9FCF-8A7E5A90A6C5}"/>
+    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="20460" activeTab="3" xr2:uid="{7EBB69BE-C1A5-8748-9FCF-8A7E5A90A6C5}"/>
   </bookViews>
   <sheets>
     <sheet name="10 hpf" sheetId="1" r:id="rId1"/>
@@ -230,10 +230,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -248,19 +261,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -285,9 +285,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -325,7 +325,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -431,7 +431,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -573,7 +573,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -585,18 +585,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="2"/>
       <c r="L1" s="11" t="s">
         <v>1</v>
@@ -612,16 +612,16 @@
       <c r="U1" s="11"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
@@ -635,16 +635,16 @@
         <v>5</v>
       </c>
       <c r="K2" s="2"/>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12" t="s">
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
       <c r="R2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2513,18 +2513,18 @@
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
       <c r="K32" s="2"/>
       <c r="L32" s="11" t="s">
         <v>1</v>
@@ -2540,16 +2540,16 @@
       <c r="U32" s="11"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12" t="s">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="1" t="s">
         <v>4</v>
       </c>
@@ -2563,16 +2563,16 @@
         <v>5</v>
       </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="12" t="s">
+      <c r="L33" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="12"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="12" t="s">
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="12"/>
-      <c r="Q33" s="12"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
       <c r="R33" s="1" t="s">
         <v>4</v>
       </c>
@@ -4452,18 +4452,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="L32:U32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="L32:U32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4475,43 +4475,43 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4525,16 +4525,16 @@
         <v>5</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15" t="s">
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
       <c r="R2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6414,43 +6414,43 @@
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="3" t="s">
         <v>4</v>
       </c>
@@ -6464,16 +6464,16 @@
         <v>5</v>
       </c>
       <c r="K33" s="4"/>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15" t="s">
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
@@ -8343,18 +8343,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="L32:U32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="L32:U32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8371,43 +8371,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -8421,16 +8421,16 @@
         <v>5</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15" t="s">
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
       <c r="R2" s="3" t="s">
         <v>4</v>
       </c>
@@ -10327,43 +10327,43 @@
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="3" t="s">
         <v>4</v>
       </c>
@@ -10377,16 +10377,16 @@
         <v>5</v>
       </c>
       <c r="K33" s="4"/>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15" t="s">
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
@@ -12256,18 +12256,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="L32:U32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="L32:U32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12279,43 +12279,43 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
+      <c r="T1" s="19"/>
+      <c r="U1" s="19"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
       <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
@@ -12329,16 +12329,16 @@
         <v>5</v>
       </c>
       <c r="K2" s="4"/>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15" t="s">
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
       <c r="R2" s="3" t="s">
         <v>4</v>
       </c>
@@ -14214,43 +14214,43 @@
       <c r="U30" s="5"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
       <c r="K32" s="4"/>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="19"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="19"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="3" t="s">
         <v>4</v>
       </c>
@@ -14264,16 +14264,16 @@
         <v>5</v>
       </c>
       <c r="K33" s="4"/>
-      <c r="L33" s="15" t="s">
+      <c r="L33" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15" t="s">
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
@@ -16185,18 +16185,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="L32:U32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="L32:U32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16208,50 +16208,50 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="K1" s="17" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="K1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="P1" s="17" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="P1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
       <c r="P2" s="11" t="s">
         <v>1</v>
       </c>
@@ -17614,73 +17614,73 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
-      <c r="S33" s="18"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="F34" s="16" t="s">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="F34" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="K34" s="17" t="s">
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="K34" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="P34" s="17" t="s">
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="P34" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
       <c r="F35" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
-      <c r="K35" s="10" t="s">
+      <c r="K35" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
       <c r="P35" s="11" t="s">
         <v>1</v>
       </c>
@@ -19440,6 +19440,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="K35:N35"/>
@@ -19450,13 +19457,6 @@
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="K34:N34"/>
     <mergeCell ref="P34:S34"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="P2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19468,101 +19468,101 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="K1" s="17" t="s">
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="K1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="P1" s="17" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="P1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="V1" s="18" t="s">
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="V1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
       <c r="P2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
-      <c r="V2" s="16" t="s">
+      <c r="V2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="AA2" s="16" t="s">
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="AA2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AF2" s="17" t="s">
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AF2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="17"/>
-      <c r="AK2" s="17" t="s">
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="14"/>
+      <c r="AK2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="17"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -19613,24 +19613,24 @@
       <c r="S3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="V3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
       <c r="AA3" s="11" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="11"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="11"/>
-      <c r="AF3" s="10" t="s">
+      <c r="AF3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
-      <c r="AI3" s="10"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
       <c r="AK3" s="11" t="s">
         <v>1</v>
       </c>
@@ -25624,6 +25624,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="P2:S2"/>
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="AA3:AD3"/>
     <mergeCell ref="AF3:AI3"/>
@@ -25632,14 +25640,6 @@
     <mergeCell ref="V2:Y2"/>
     <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="AF2:AI2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="P2:S2"/>
     <mergeCell ref="AK2:AN2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25652,143 +25652,143 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="U1" s="18" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="U1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AA1" s="18"/>
-      <c r="AB1" s="18"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AJ1" s="18"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="F2" s="16" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="K2" s="17" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="K2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="P2" s="17" t="s">
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="P2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="U2" s="16" t="s">
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="U2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Z2" s="16" t="s">
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Z2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AE2" s="17" t="s">
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AE2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
-      <c r="AJ2" s="17" t="s">
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AJ2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="AK2" s="17"/>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="20"/>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="10"/>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="F3" s="11" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
       <c r="P3" s="11" t="s">
         <v>1</v>
       </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
-      <c r="U3" s="10" t="s">
+      <c r="U3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
       <c r="Z3" s="11" t="s">
         <v>1</v>
       </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
       <c r="AC3" s="11"/>
-      <c r="AE3" s="10" t="s">
+      <c r="AE3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="AF3" s="10"/>
-      <c r="AG3" s="10"/>
-      <c r="AH3" s="10"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
       <c r="AJ3" s="11" t="s">
         <v>1</v>
       </c>
@@ -25942,35 +25942,35 @@
         <v>0.65026706000000001</v>
       </c>
       <c r="U5">
-        <f>A5/$A$31</f>
+        <f t="shared" ref="U5:U29" si="0">A5/$A$31</f>
         <v>1.0563851975384113</v>
       </c>
       <c r="V5">
-        <f>B5/$B$31</f>
+        <f t="shared" ref="V5:V29" si="1">B5/$B$31</f>
         <v>0.7465791043547868</v>
       </c>
       <c r="W5">
-        <f>C5/$C$31</f>
+        <f t="shared" ref="W5:W29" si="2">C5/$C$31</f>
         <v>1.4278342252325029</v>
       </c>
       <c r="X5">
-        <f>D5/$D$31</f>
+        <f t="shared" ref="X5:X16" si="3">D5/$D$31</f>
         <v>0.8713068813757876</v>
       </c>
       <c r="Z5">
-        <f>F5/$A$31</f>
+        <f t="shared" ref="Z5:Z29" si="4">F5/$A$31</f>
         <v>1.2057631985434758</v>
       </c>
       <c r="AA5">
-        <f>G5/$B$31</f>
+        <f t="shared" ref="AA5:AA29" si="5">G5/$B$31</f>
         <v>0.77262222933249025</v>
       </c>
       <c r="AB5">
-        <f>H5/$C$31</f>
+        <f t="shared" ref="AB5:AB13" si="6">H5/$C$31</f>
         <v>0.75877730484867179</v>
       </c>
       <c r="AC5">
-        <f>I5/$D$31</f>
+        <f t="shared" ref="AC5:AC27" si="7">I5/$D$31</f>
         <v>0.781980928077047</v>
       </c>
       <c r="AE5">
@@ -25978,23 +25978,23 @@
         <v>0.96349700150528783</v>
       </c>
       <c r="AF5">
-        <f>L5/$L$31</f>
+        <f t="shared" ref="AF5:AF16" si="8">L5/$L$31</f>
         <v>0.81966106485458634</v>
       </c>
       <c r="AH5">
-        <f>N5/$N$31</f>
+        <f t="shared" ref="AH5:AH29" si="9">N5/$N$31</f>
         <v>0.62070943871660533</v>
       </c>
       <c r="AJ5">
-        <f>P5/$K$31</f>
+        <f t="shared" ref="AJ5:AJ22" si="10">P5/$K$31</f>
         <v>2.0545689122462738</v>
       </c>
       <c r="AK5">
-        <f>Q5/$L$31</f>
+        <f t="shared" ref="AK5:AK29" si="11">Q5/$L$31</f>
         <v>0.51424970897369049</v>
       </c>
       <c r="AL5">
-        <f>R5/$M$31</f>
+        <f t="shared" ref="AL5:AL14" si="12">R5/$M$31</f>
         <v>0.54066725162240437</v>
       </c>
       <c r="AM5">
@@ -26052,35 +26052,35 @@
         <v>0.38934027999999998</v>
       </c>
       <c r="U6">
-        <f>A6/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.92741138271359447</v>
       </c>
       <c r="V6">
-        <f>B6/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.56558761347398434</v>
       </c>
       <c r="W6">
-        <f>C6/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.83154247788911795</v>
       </c>
       <c r="X6">
-        <f>D6/$D$31</f>
+        <f t="shared" si="3"/>
         <v>1.1349599400304662</v>
       </c>
       <c r="Z6">
-        <f>F6/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.80842959699661598</v>
       </c>
       <c r="AA6">
-        <f>G6/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.85291764373807311</v>
       </c>
       <c r="AB6">
-        <f>H6/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.80700497464886001</v>
       </c>
       <c r="AC6">
-        <f>I6/$D$31</f>
+        <f t="shared" si="7"/>
         <v>1.0059241709756361</v>
       </c>
       <c r="AE6">
@@ -26088,27 +26088,27 @@
         <v>1.1123289592342918</v>
       </c>
       <c r="AF6">
-        <f>L6/$L$31</f>
+        <f t="shared" si="8"/>
         <v>0.29774480958249711</v>
       </c>
       <c r="AG6">
-        <f>M6/$M$31</f>
+        <f t="shared" ref="AG6:AG15" si="13">M6/$M$31</f>
         <v>0.66867098395131697</v>
       </c>
       <c r="AH6">
-        <f>N6/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.5838889494169111</v>
       </c>
       <c r="AJ6">
-        <f>P6/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.90742612334447992</v>
       </c>
       <c r="AK6">
-        <f>Q6/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.4388193389334466</v>
       </c>
       <c r="AL6">
-        <f>R6/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.49119357255694418</v>
       </c>
       <c r="AM6">
@@ -26166,35 +26166,35 @@
         <v>0.34933007999999999</v>
       </c>
       <c r="U7">
-        <f>A7/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.7715065018663827</v>
       </c>
       <c r="V7">
-        <f>B7/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.479727785935256</v>
       </c>
       <c r="W7">
-        <f>C7/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.1316398770692546</v>
       </c>
       <c r="X7">
-        <f>D7/$D$31</f>
+        <f t="shared" si="3"/>
         <v>1.1471386857630375</v>
       </c>
       <c r="Z7">
-        <f>F7/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.0727513902219254</v>
       </c>
       <c r="AA7">
-        <f>G7/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.93898227425456782</v>
       </c>
       <c r="AB7">
-        <f>H7/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.71432474682269065</v>
       </c>
       <c r="AC7">
-        <f>I7/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.60693546506754448</v>
       </c>
       <c r="AE7">
@@ -26202,27 +26202,27 @@
         <v>0.88758671530212441</v>
       </c>
       <c r="AF7">
-        <f>L7/$L$31</f>
+        <f t="shared" si="8"/>
         <v>0.7064814190846187</v>
       </c>
       <c r="AG7">
-        <f>M7/$M$31</f>
+        <f t="shared" si="13"/>
         <v>1.6514333419113614</v>
       </c>
       <c r="AH7">
-        <f>N7/$N$31</f>
+        <f t="shared" si="9"/>
         <v>2.61368612137837</v>
       </c>
       <c r="AJ7">
-        <f>P7/$K$31</f>
+        <f t="shared" si="10"/>
         <v>1.4313995707551135</v>
       </c>
       <c r="AK7">
-        <f>Q7/$L$31</f>
+        <f t="shared" si="11"/>
         <v>1.3751308588058828</v>
       </c>
       <c r="AL7">
-        <f>R7/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.52424539963865202</v>
       </c>
       <c r="AM7">
@@ -26280,35 +26280,35 @@
         <v>0.34557462999999999</v>
       </c>
       <c r="U8">
-        <f>A8/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.81382761519561875</v>
       </c>
       <c r="V8">
-        <f>B8/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.88109364746579244</v>
       </c>
       <c r="W8">
-        <f>C8/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.97346840217368613</v>
       </c>
       <c r="X8">
-        <f>D8/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.82356570320846301</v>
       </c>
       <c r="Z8">
-        <f>F8/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.74929396159625594</v>
       </c>
       <c r="AA8">
-        <f>G8/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.92211692356656716</v>
       </c>
       <c r="AB8">
-        <f>H8/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.8162831708128746</v>
       </c>
       <c r="AC8">
-        <f>I8/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.6174077484534426</v>
       </c>
       <c r="AE8">
@@ -26316,27 +26316,27 @@
         <v>0.71309514015745534</v>
       </c>
       <c r="AF8">
-        <f>L8/$L$31</f>
+        <f t="shared" si="8"/>
         <v>0.80574525984664991</v>
       </c>
       <c r="AG8">
-        <f>M8/$M$31</f>
+        <f t="shared" si="13"/>
         <v>1.0232529877756431</v>
       </c>
       <c r="AH8">
-        <f>N8/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.82098774268457242</v>
       </c>
       <c r="AJ8">
-        <f>P8/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.67832250926193549</v>
       </c>
       <c r="AK8">
-        <f>Q8/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.7141390809086805</v>
       </c>
       <c r="AL8">
-        <f>R8/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.47325271424653853</v>
       </c>
       <c r="AM8">
@@ -26394,35 +26394,35 @@
         <v>0.25850592</v>
       </c>
       <c r="U9">
-        <f>A9/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.73612048827264276</v>
       </c>
       <c r="V9">
-        <f>B9/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.79466542693967201</v>
       </c>
       <c r="W9">
-        <f>C9/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.82505892934652048</v>
       </c>
       <c r="X9">
-        <f>D9/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.83169279202656787</v>
       </c>
       <c r="Z9">
-        <f>F9/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.91528599145203327</v>
       </c>
       <c r="AA9">
-        <f>G9/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.93058636483535795</v>
       </c>
       <c r="AB9">
-        <f>H9/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.70627990971696797</v>
       </c>
       <c r="AC9">
-        <f>I9/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.62316756635834891</v>
       </c>
       <c r="AE9">
@@ -26430,27 +26430,27 @@
         <v>1.0713995900490603</v>
       </c>
       <c r="AF9">
-        <f>L9/$L$31</f>
+        <f t="shared" si="8"/>
         <v>1.3595044023765848</v>
       </c>
       <c r="AG9">
-        <f>M9/$M$31</f>
+        <f t="shared" si="13"/>
         <v>0.58610295025410286</v>
       </c>
       <c r="AH9">
-        <f>N9/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.68464425278376428</v>
       </c>
       <c r="AJ9">
-        <f>P9/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.85061726056434617</v>
       </c>
       <c r="AK9">
-        <f>Q9/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.68207997121732356</v>
       </c>
       <c r="AL9">
-        <f>R9/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.3841923608153433</v>
       </c>
       <c r="AM9">
@@ -26504,59 +26504,59 @@
       </c>
       <c r="S10" s="7"/>
       <c r="U10">
-        <f>A10/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.3326148811496175</v>
       </c>
       <c r="V10">
-        <f>B10/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.1293280694066756</v>
       </c>
       <c r="W10">
-        <f>C10/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.93909884185352643</v>
       </c>
       <c r="X10">
-        <f>D10/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.90768549406966559</v>
       </c>
       <c r="Z10">
-        <f>F10/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.80724892574974816</v>
       </c>
       <c r="AA10">
-        <f>G10/$B$31</f>
+        <f t="shared" si="5"/>
         <v>1.1859363853310045</v>
       </c>
       <c r="AB10">
-        <f>H10/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.75355787614227332</v>
       </c>
       <c r="AC10">
-        <f>I10/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.89007917792464397</v>
       </c>
       <c r="AF10">
-        <f>L10/$L$31</f>
+        <f t="shared" si="8"/>
         <v>1.8963931362276212</v>
       </c>
       <c r="AG10">
-        <f>M10/$M$31</f>
+        <f t="shared" si="13"/>
         <v>0.64791492071863532</v>
       </c>
       <c r="AH10">
-        <f>N10/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.0597237059488851</v>
       </c>
       <c r="AJ10">
-        <f>P10/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.52354048858657731</v>
       </c>
       <c r="AK10">
-        <f>Q10/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.73578447926378177</v>
       </c>
       <c r="AL10">
-        <f>R10/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.53732222765295512</v>
       </c>
     </row>
@@ -26610,35 +26610,35 @@
         <v>0.18288674999999999</v>
       </c>
       <c r="U11">
-        <f>A11/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.7444478919923091</v>
       </c>
       <c r="V11">
-        <f>B11/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.0772934345262655</v>
       </c>
       <c r="W11">
-        <f>C11/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.0168668523938684</v>
       </c>
       <c r="X11">
-        <f>D11/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.81395268660247622</v>
       </c>
       <c r="Z11">
-        <f>F11/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.1304706794502797</v>
       </c>
       <c r="AA11">
-        <f>G11/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.87399340671602033</v>
       </c>
       <c r="AB11">
-        <f>H11/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.65657837928471297</v>
       </c>
       <c r="AC11">
-        <f>I11/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.5446047199195857</v>
       </c>
       <c r="AE11">
@@ -26646,31 +26646,31 @@
         <v>0.93053652802309805</v>
       </c>
       <c r="AF11">
-        <f>L11/$L$31</f>
+        <f t="shared" si="8"/>
         <v>1.3111040513517587</v>
       </c>
       <c r="AG11">
-        <f>M11/$M$31</f>
+        <f t="shared" si="13"/>
         <v>2.248120575169684</v>
       </c>
       <c r="AH11">
-        <f>N11/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.69679940981557531</v>
       </c>
       <c r="AJ11">
-        <f>P11/$K$31</f>
+        <f t="shared" si="10"/>
         <v>1.5238289227675521</v>
       </c>
       <c r="AK11">
-        <f>Q11/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.56483234361421808</v>
       </c>
       <c r="AL11">
-        <f>R11/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.34106913587490828</v>
       </c>
       <c r="AM11">
-        <f>S11/$N$31</f>
+        <f t="shared" ref="AM11:AM27" si="14">S11/$N$31</f>
         <v>0.18012974145849411</v>
       </c>
     </row>
@@ -26724,35 +26724,35 @@
         <v>0.75394592000000005</v>
       </c>
       <c r="U12">
-        <f>A12/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.79219914004976677</v>
       </c>
       <c r="V12">
-        <f>B12/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.86738334855089239</v>
       </c>
       <c r="W12">
-        <f>C12/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.98509444618162201</v>
       </c>
       <c r="X12">
-        <f>D12/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.50050154879178776</v>
       </c>
       <c r="Z12">
-        <f>F12/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.347290625019439</v>
       </c>
       <c r="AA12">
-        <f>G12/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.86117107627495237</v>
       </c>
       <c r="AB12">
-        <f>H12/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.74890561970806158</v>
       </c>
       <c r="AC12">
-        <f>I12/$D$31</f>
+        <f t="shared" si="7"/>
         <v>1.1431126410233763</v>
       </c>
       <c r="AE12">
@@ -26760,31 +26760,31 @@
         <v>0.88759613216429178</v>
       </c>
       <c r="AF12">
-        <f>L12/$L$31</f>
+        <f t="shared" si="8"/>
         <v>0.64936914883904406</v>
       </c>
       <c r="AG12">
-        <f>M12/$M$31</f>
+        <f t="shared" si="13"/>
         <v>1.3126772581152502</v>
       </c>
       <c r="AH12">
-        <f>N12/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.24834419275908282</v>
       </c>
       <c r="AJ12">
-        <f>P12/$K$31</f>
+        <f t="shared" si="10"/>
         <v>2.8582561250448846</v>
       </c>
       <c r="AK12">
-        <f>Q12/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.54517215965652077</v>
       </c>
       <c r="AL12">
-        <f>R12/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.8457843164595571</v>
       </c>
       <c r="AM12">
-        <f>S12/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.74258022324354556</v>
       </c>
     </row>
@@ -26836,63 +26836,63 @@
         <v>0.49515418</v>
       </c>
       <c r="U13">
-        <f>A13/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.0906306312959131</v>
       </c>
       <c r="V13">
-        <f>B13/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.2034171636896764</v>
       </c>
       <c r="W13">
-        <f>C13/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.96635159749915212</v>
       </c>
       <c r="X13">
-        <f>D13/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.86637138155883076</v>
       </c>
       <c r="Z13">
-        <f>F13/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.0829449614007911</v>
       </c>
       <c r="AA13">
-        <f>G13/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.85121432841563816</v>
       </c>
       <c r="AB13">
-        <f>H13/$C$31</f>
+        <f t="shared" si="6"/>
         <v>0.88388414267063053</v>
       </c>
       <c r="AC13">
-        <f>I13/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.6810112114787904</v>
       </c>
       <c r="AF13">
-        <f>L13/$L$31</f>
+        <f t="shared" si="8"/>
         <v>1.5285687256561789</v>
       </c>
       <c r="AG13">
-        <f>M13/$M$31</f>
+        <f t="shared" si="13"/>
         <v>0.99474192055767052</v>
       </c>
       <c r="AH13">
-        <f>N13/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.48127582526421842</v>
       </c>
       <c r="AJ13">
-        <f>P13/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.93777298390394537</v>
       </c>
       <c r="AK13">
-        <f>Q13/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.56114699822115466</v>
       </c>
       <c r="AL13">
-        <f>R13/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.61133125049409887</v>
       </c>
       <c r="AM13">
-        <f>S13/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.48768975568483042</v>
       </c>
     </row>
@@ -26944,31 +26944,31 @@
         <v>0.28698192</v>
       </c>
       <c r="U14">
-        <f>A14/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.99171080807832446</v>
       </c>
       <c r="V14">
-        <f>B14/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.90493583211377715</v>
       </c>
       <c r="W14">
-        <f>C14/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.0571814633428633</v>
       </c>
       <c r="X14">
-        <f>D14/$D$31</f>
+        <f t="shared" si="3"/>
         <v>0.85281778247473983</v>
       </c>
       <c r="Z14">
-        <f>F14/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.0161757098380553</v>
       </c>
       <c r="AA14">
-        <f>G14/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.81710921249924162</v>
       </c>
       <c r="AC14">
-        <f>I14/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.61971069377521382</v>
       </c>
       <c r="AE14">
@@ -26976,31 +26976,31 @@
         <v>1.4139862437816628</v>
       </c>
       <c r="AF14">
-        <f>L14/$L$31</f>
+        <f t="shared" si="8"/>
         <v>1.0704329538995829</v>
       </c>
       <c r="AG14">
-        <f>M14/$M$31</f>
+        <f t="shared" si="13"/>
         <v>1.0589165398320135</v>
       </c>
       <c r="AH14">
-        <f>N14/$N$31</f>
+        <f t="shared" si="9"/>
         <v>2.0605527055446937</v>
       </c>
       <c r="AJ14">
-        <f>P14/$K$31</f>
+        <f t="shared" si="10"/>
         <v>1.3543752139998155</v>
       </c>
       <c r="AK14">
-        <f>Q14/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.43978789764708043</v>
       </c>
       <c r="AL14">
-        <f>R14/$M$31</f>
+        <f t="shared" si="12"/>
         <v>0.75928946519929097</v>
       </c>
       <c r="AM14">
-        <f>S14/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.28265568201557656</v>
       </c>
     </row>
@@ -27050,59 +27050,59 @@
         <v>0.38423473000000002</v>
       </c>
       <c r="U15">
-        <f>A15/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.2373326707895895</v>
       </c>
       <c r="V15">
-        <f>B15/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.0327951895641052</v>
       </c>
       <c r="W15">
-        <f>C15/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.2042160413687599</v>
       </c>
       <c r="X15">
-        <f>D15/$D$31</f>
+        <f t="shared" si="3"/>
         <v>1.2434166338305919</v>
       </c>
       <c r="Z15">
-        <f>F15/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.85394571726511459</v>
       </c>
       <c r="AA15">
-        <f>G15/$B$31</f>
+        <f t="shared" si="5"/>
         <v>1.1033632772658191</v>
       </c>
       <c r="AB15">
-        <f>H15/$C$31</f>
+        <f t="shared" ref="AB15:AB29" si="15">H15/$C$31</f>
         <v>1.0198471078924698</v>
       </c>
       <c r="AC15">
-        <f>I15/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.66530664750155455</v>
       </c>
       <c r="AF15">
-        <f>L15/$L$31</f>
+        <f t="shared" si="8"/>
         <v>2.2318484872452111</v>
       </c>
       <c r="AG15">
-        <f>M15/$M$31</f>
+        <f t="shared" si="13"/>
         <v>0.83928719289578235</v>
       </c>
       <c r="AH15">
-        <f>N15/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.6300466542646617</v>
       </c>
       <c r="AJ15">
-        <f>P15/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.77157989463817511</v>
       </c>
       <c r="AK15">
-        <f>Q15/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.78118202897357969</v>
       </c>
       <c r="AM15">
-        <f>S15/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.37844241080490687</v>
       </c>
     </row>
@@ -27154,63 +27154,63 @@
         <v>0.19663016</v>
       </c>
       <c r="U16">
-        <f>A16/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.2171767457418767</v>
       </c>
       <c r="V16">
-        <f>B16/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.74458983580565719</v>
       </c>
       <c r="W16">
-        <f>C16/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.2344396566705829</v>
       </c>
       <c r="X16">
-        <f>D16/$D$31</f>
+        <f t="shared" si="3"/>
         <v>1.5304026066048004</v>
       </c>
       <c r="Z16">
-        <f>F16/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.80072786883688474</v>
       </c>
       <c r="AA16">
-        <f>G16/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.7655890150053154</v>
       </c>
       <c r="AB16">
-        <f>H16/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.49917891437141432</v>
       </c>
       <c r="AC16">
-        <f>I16/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.42503474565408639</v>
       </c>
       <c r="AE16">
-        <f>K16/$K$31</f>
+        <f t="shared" ref="AE16:AE28" si="16">K16/$K$31</f>
         <v>0.80954846606130137</v>
       </c>
       <c r="AF16">
-        <f>L16/$L$31</f>
+        <f t="shared" si="8"/>
         <v>0.48953378091704269</v>
       </c>
       <c r="AH16">
-        <f>N16/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.8502416201389884</v>
       </c>
       <c r="AJ16">
-        <f>P16/$K$31</f>
+        <f t="shared" si="10"/>
         <v>1.5301849020357519</v>
       </c>
       <c r="AK16">
-        <f>Q16/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.51133899913628067</v>
       </c>
       <c r="AL16">
-        <f>R16/$M$31</f>
+        <f t="shared" ref="AL16:AL29" si="17">R16/$M$31</f>
         <v>0.16890447103853287</v>
       </c>
       <c r="AM16">
-        <f>S16/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.19366597024520549</v>
       </c>
     </row>
@@ -27260,59 +27260,59 @@
         <v>0.26802376</v>
       </c>
       <c r="U17">
-        <f>A17/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.91334255263621655</v>
       </c>
       <c r="V17">
-        <f>B17/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.4023654534937362</v>
       </c>
       <c r="W17">
-        <f>C17/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.7754281285347302</v>
       </c>
       <c r="Z17">
-        <f>F17/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.77121272423382314</v>
       </c>
       <c r="AA17">
-        <f>G17/$B$31</f>
+        <f t="shared" si="5"/>
         <v>1.0415481478708846</v>
       </c>
       <c r="AB17">
-        <f>H17/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.65174579361460838</v>
       </c>
       <c r="AC17">
-        <f>I17/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.57358702202852119</v>
       </c>
       <c r="AE17">
-        <f>K17/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.1842749633006415</v>
       </c>
       <c r="AG17">
-        <f>M17/$M$31</f>
+        <f t="shared" ref="AG17:AG28" si="18">M17/$M$31</f>
         <v>1.077307688903711</v>
       </c>
       <c r="AH17">
-        <f>N17/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.9698136191460816</v>
       </c>
       <c r="AJ17">
-        <f>P17/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.60282947678704246</v>
       </c>
       <c r="AK17">
-        <f>Q17/$L$31</f>
+        <f t="shared" si="11"/>
         <v>1.1903318294535805</v>
       </c>
       <c r="AL17">
-        <f>R17/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.41515591970669158</v>
       </c>
       <c r="AM17">
-        <f>S17/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.26398331532237013</v>
       </c>
     </row>
@@ -27366,67 +27366,67 @@
         <v>0.38225298000000002</v>
       </c>
       <c r="U18">
-        <f>A18/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.8029500849130834</v>
       </c>
       <c r="V18">
-        <f>B18/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.2293253345216024</v>
       </c>
       <c r="W18">
-        <f>C18/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.80230266501125724</v>
       </c>
       <c r="X18">
-        <f>D18/$D$31</f>
+        <f t="shared" ref="X18:X29" si="19">D18/$D$31</f>
         <v>0.76967771151188358</v>
       </c>
       <c r="Z18">
-        <f>F18/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.0090316989517698</v>
       </c>
       <c r="AA18">
-        <f>G18/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.97542725572328881</v>
       </c>
       <c r="AB18">
-        <f>H18/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.706280709511103</v>
       </c>
       <c r="AC18">
-        <f>I18/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.71475451088725217</v>
       </c>
       <c r="AE18">
-        <f>K18/$K$31</f>
+        <f t="shared" si="16"/>
         <v>0.88581268998526808</v>
       </c>
       <c r="AF18">
-        <f>L18/$L$31</f>
+        <f t="shared" ref="AF18:AF29" si="20">L18/$L$31</f>
         <v>1.7007269853260829</v>
       </c>
       <c r="AG18">
-        <f>M18/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.89510510842028068</v>
       </c>
       <c r="AH18">
-        <f>N18/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.40874932284679183</v>
       </c>
       <c r="AJ18">
-        <f>P18/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.78559066769370267</v>
       </c>
       <c r="AK18">
-        <f>Q18/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.75590665588700579</v>
       </c>
       <c r="AL18">
-        <f>R18/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.4346294567823939</v>
       </c>
       <c r="AM18">
-        <f>S18/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.37649053558630646</v>
       </c>
     </row>
@@ -27480,67 +27480,67 @@
         <v>0.35584700000000002</v>
       </c>
       <c r="U19">
-        <f>A19/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.0023240099219</v>
       </c>
       <c r="V19">
-        <f>B19/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.83321285710900705</v>
       </c>
       <c r="W19">
-        <f>C19/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.88737086258920228</v>
       </c>
       <c r="X19">
-        <f>D19/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.99859933594719452</v>
       </c>
       <c r="Z19">
-        <f>F19/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.2318354729146288</v>
       </c>
       <c r="AA19">
-        <f>G19/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.97302507549795214</v>
       </c>
       <c r="AB19">
-        <f>H19/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.79917362693934224</v>
       </c>
       <c r="AC19">
-        <f>I19/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.78695930359020949</v>
       </c>
       <c r="AE19">
-        <f>K19/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.1589237171444369</v>
       </c>
       <c r="AF19">
-        <f>L19/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.95377139958093238</v>
       </c>
       <c r="AG19">
-        <f>M19/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.74473154737443159</v>
       </c>
       <c r="AH19">
-        <f>N19/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.37009251170525814</v>
       </c>
       <c r="AJ19">
-        <f>P19/$K$31</f>
+        <f t="shared" si="10"/>
         <v>2.3277875828134409</v>
       </c>
       <c r="AK19">
-        <f>Q19/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.77308185488947812</v>
       </c>
       <c r="AL19">
-        <f>R19/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.58739137275066156</v>
       </c>
       <c r="AM19">
-        <f>S19/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.35048262440434186</v>
       </c>
     </row>
@@ -27594,67 +27594,67 @@
         <v>0.31759575000000001</v>
       </c>
       <c r="U20">
-        <f>A20/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.1308262578928645</v>
       </c>
       <c r="V20">
-        <f>B20/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.0339891629716715</v>
       </c>
       <c r="W20">
-        <f>C20/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.0102848943990019</v>
       </c>
       <c r="X20">
-        <f>D20/$D$31</f>
+        <f t="shared" si="19"/>
         <v>1.6114567430223949</v>
       </c>
       <c r="Z20">
-        <f>F20/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.2887168028350182</v>
       </c>
       <c r="AA20">
-        <f>G20/$B$31</f>
+        <f t="shared" si="5"/>
         <v>1.0811173673412739</v>
       </c>
       <c r="AB20">
-        <f>H20/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.54368348683510004</v>
       </c>
       <c r="AC20">
-        <f>I20/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.8432814277099453</v>
       </c>
       <c r="AE20">
-        <f>K20/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.0218896627911935</v>
       </c>
       <c r="AF20">
-        <f>L20/$L$31</f>
+        <f t="shared" si="20"/>
         <v>1.623694993730846</v>
       </c>
       <c r="AG20">
-        <f>M20/$M$31</f>
+        <f t="shared" si="18"/>
         <v>1.4057566979874401</v>
       </c>
       <c r="AH20">
-        <f>N20/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.88731635799118891</v>
       </c>
       <c r="AJ20">
-        <f>P20/$K$31</f>
+        <f t="shared" si="10"/>
         <v>1.9957280207118104</v>
       </c>
       <c r="AK20">
-        <f>Q20/$L$31</f>
+        <f t="shared" si="11"/>
         <v>1.0094629341555377</v>
       </c>
       <c r="AL20">
-        <f>R20/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.27292600693612706</v>
       </c>
       <c r="AM20">
-        <f>S20/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.31280801007080361</v>
       </c>
     </row>
@@ -27708,67 +27708,67 @@
         <v>0.25900684000000002</v>
       </c>
       <c r="U21">
-        <f>A21/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.96769772584704772</v>
       </c>
       <c r="V21">
-        <f>B21/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.91657662888008418</v>
       </c>
       <c r="W21">
-        <f>C21/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.7741291029005849</v>
       </c>
       <c r="X21">
-        <f>D21/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.77092544968821008</v>
       </c>
       <c r="Z21">
-        <f>F21/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.8203675604613927</v>
       </c>
       <c r="AA21">
-        <f>G21/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.75817551429830055</v>
       </c>
       <c r="AB21">
-        <f>H21/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.63249097931946507</v>
       </c>
       <c r="AC21">
-        <f>I21/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.79082041724841468</v>
       </c>
       <c r="AE21">
-        <f>K21/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.2613152729638875</v>
       </c>
       <c r="AF21">
-        <f>L21/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.92181170539561319</v>
       </c>
       <c r="AG21">
-        <f>M21/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.4449759261123481</v>
       </c>
       <c r="AH21">
-        <f>N21/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.48353724272765386</v>
       </c>
       <c r="AJ21">
-        <f>P21/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.89313244172916806</v>
       </c>
       <c r="AK21">
-        <f>Q21/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.58476477504756386</v>
       </c>
       <c r="AL21">
-        <f>R21/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.28744060996124182</v>
       </c>
       <c r="AM21">
-        <f>S21/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.25510232493705287</v>
       </c>
     </row>
@@ -27822,67 +27822,67 @@
         <v>0.24256662000000001</v>
       </c>
       <c r="U22">
-        <f>A22/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.98059574025662544</v>
       </c>
       <c r="V22">
-        <f>B22/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.84499236492748397</v>
       </c>
       <c r="W22">
-        <f>C22/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.0922990676401678</v>
       </c>
       <c r="X22">
-        <f>D22/$D$31</f>
+        <f t="shared" si="19"/>
         <v>1.1872639946032604</v>
       </c>
       <c r="Z22">
-        <f>F22/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.0532854190016636</v>
       </c>
       <c r="AA22">
-        <f>G22/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.99064456490879416</v>
       </c>
       <c r="AB22">
-        <f>H22/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.70868183059915002</v>
       </c>
       <c r="AC22">
-        <f>I22/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.64071162299283668</v>
       </c>
       <c r="AE22">
-        <f>K22/$K$31</f>
+        <f t="shared" si="16"/>
         <v>0.93958204366524656</v>
       </c>
       <c r="AF22">
-        <f>L22/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.65061413299642812</v>
       </c>
       <c r="AG22">
-        <f>M22/$M$31</f>
+        <f t="shared" si="18"/>
         <v>1.3500051684987522</v>
       </c>
       <c r="AH22">
-        <f>N22/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.71826532927843911</v>
       </c>
       <c r="AJ22">
-        <f>P22/$K$31</f>
+        <f t="shared" si="10"/>
         <v>0.84385982559322248</v>
       </c>
       <c r="AK22">
-        <f>Q22/$L$31</f>
+        <f t="shared" si="11"/>
         <v>1.2408910825738275</v>
       </c>
       <c r="AL22">
-        <f>R22/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.431217741517047</v>
       </c>
       <c r="AM22">
-        <f>S22/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.23890994042521282</v>
       </c>
     </row>
@@ -27934,63 +27934,63 @@
         <v>0.29993762000000002</v>
       </c>
       <c r="U23">
-        <f>A23/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.91363161948281812</v>
       </c>
       <c r="V23">
-        <f>B23/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.93015856831387134</v>
       </c>
       <c r="W23">
-        <f>C23/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.2157823929152949</v>
       </c>
       <c r="X23">
-        <f>D23/$D$31</f>
+        <f t="shared" si="19"/>
         <v>1.0582173349529342</v>
       </c>
       <c r="Z23">
-        <f>F23/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.3201410725634728</v>
       </c>
       <c r="AA23">
-        <f>G23/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.76154423677605665</v>
       </c>
       <c r="AB23">
-        <f>H23/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.69435426978077464</v>
       </c>
       <c r="AC23">
-        <f>I23/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.77683101966126533</v>
       </c>
       <c r="AE23">
-        <f>K23/$K$31</f>
+        <f t="shared" si="16"/>
         <v>0.85235055175702468</v>
       </c>
       <c r="AF23">
-        <f>L23/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.80563436751257322</v>
       </c>
       <c r="AG23">
-        <f>M23/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.88826496891639151</v>
       </c>
       <c r="AH23">
-        <f>N23/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.3881788460236357</v>
       </c>
       <c r="AK23">
-        <f>Q23/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.50870692956908481</v>
       </c>
       <c r="AL23">
-        <f>R23/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.34789335365530072</v>
       </c>
       <c r="AM23">
-        <f>S23/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.29541607549084919</v>
       </c>
     </row>
@@ -28044,67 +28044,67 @@
         <v>0.35617717999999998</v>
       </c>
       <c r="U24">
-        <f>A24/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.0417872223250682</v>
       </c>
       <c r="V24">
-        <f>B24/$B$31</f>
+        <f t="shared" si="1"/>
         <v>0.91004094139874314</v>
       </c>
       <c r="W24">
-        <f>C24/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.80495604116949848</v>
       </c>
       <c r="X24">
-        <f>D24/$D$31</f>
+        <f t="shared" si="19"/>
         <v>1.1279223986702631</v>
       </c>
       <c r="Z24">
-        <f>F24/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.1161696736304234</v>
       </c>
       <c r="AA24">
-        <f>G24/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.75904949922743692</v>
       </c>
       <c r="AB24">
-        <f>H24/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.67147151974173647</v>
       </c>
       <c r="AC24">
-        <f>I24/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.70015473999690003</v>
       </c>
       <c r="AE24">
-        <f>K24/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.0866839317596817</v>
       </c>
       <c r="AF24">
-        <f>L24/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.58604001172096243</v>
       </c>
       <c r="AG24">
-        <f>M24/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.55949013485535504</v>
       </c>
       <c r="AH24">
-        <f>N24/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.48732620999948284</v>
       </c>
       <c r="AJ24">
-        <f>P24/$K$31</f>
+        <f t="shared" ref="AJ24:AJ29" si="21">P24/$K$31</f>
         <v>1.2120254648591824</v>
       </c>
       <c r="AK24">
-        <f>Q24/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.38267847144003309</v>
       </c>
       <c r="AL24">
-        <f>R24/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.35552633393730509</v>
       </c>
       <c r="AM24">
-        <f>S24/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.35080782695747792</v>
       </c>
     </row>
@@ -28158,67 +28158,67 @@
         <v>0.47172024000000001</v>
       </c>
       <c r="U25">
-        <f>A25/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.2892254049658074</v>
       </c>
       <c r="V25">
-        <f>B25/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.0104899901239515</v>
       </c>
       <c r="W25">
-        <f>C25/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.93596740439920634</v>
       </c>
       <c r="X25">
-        <f>D25/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.90450103093935397</v>
       </c>
       <c r="Z25">
-        <f>F25/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.72660565002799615</v>
       </c>
       <c r="AA25">
-        <f>G25/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.9141388785148894</v>
       </c>
       <c r="AB25">
-        <f>H25/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.72760074526703622</v>
       </c>
       <c r="AC25">
-        <f>I25/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.91748133775225116</v>
       </c>
       <c r="AE25">
-        <f>K25/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.0044220339776793</v>
       </c>
       <c r="AF25">
-        <f>L25/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.73436643662044432</v>
       </c>
       <c r="AG25">
-        <f>M25/$M$31</f>
+        <f t="shared" si="18"/>
         <v>1.0616785652338316</v>
       </c>
       <c r="AH25">
-        <f>N25/$N$31</f>
+        <f t="shared" si="9"/>
         <v>1.0077723075325016</v>
       </c>
       <c r="AJ25">
-        <f>P25/$K$31</f>
+        <f t="shared" si="21"/>
         <v>0.79987555197725291</v>
       </c>
       <c r="AK25">
-        <f>Q25/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.68154431040339869</v>
       </c>
       <c r="AL25">
-        <f>R25/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.44382816425071686</v>
       </c>
       <c r="AM25">
-        <f>S25/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.46460908114961197</v>
       </c>
     </row>
@@ -28272,67 +28272,67 @@
         <v>0.21369125</v>
       </c>
       <c r="U26">
-        <f>A26/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.232398958866465</v>
       </c>
       <c r="V26">
-        <f>B26/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.0280810484094582</v>
       </c>
       <c r="W26">
-        <f>C26/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.93601410542196162</v>
       </c>
       <c r="X26">
-        <f>D26/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.8446103634677341</v>
       </c>
       <c r="Z26">
-        <f>F26/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.71209681807522984</v>
       </c>
       <c r="AA26">
-        <f>G26/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.9660411114472135</v>
       </c>
       <c r="AB26">
-        <f>H26/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.60175233136832917</v>
       </c>
       <c r="AC26">
-        <f>I26/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.73704095804610747</v>
       </c>
       <c r="AE26">
-        <f>K26/$K$31</f>
+        <f t="shared" si="16"/>
         <v>0.79233815920181405</v>
       </c>
       <c r="AF26">
-        <f>L26/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.83096674721210306</v>
       </c>
       <c r="AG26">
-        <f>M26/$M$31</f>
+        <f t="shared" si="18"/>
         <v>1.0572991915583139</v>
       </c>
       <c r="AH26">
-        <f>N26/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.55269470066848314</v>
       </c>
       <c r="AJ26">
-        <f>P26/$K$31</f>
+        <f t="shared" si="21"/>
         <v>1.3776072015205614</v>
       </c>
       <c r="AK26">
-        <f>Q26/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.78319110309243267</v>
       </c>
       <c r="AL26">
-        <f>R26/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.31988495340305917</v>
       </c>
       <c r="AM26">
-        <f>S26/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.21046986517307806</v>
       </c>
     </row>
@@ -28386,67 +28386,67 @@
         <v>0.37912491999999998</v>
       </c>
       <c r="U27">
-        <f>A27/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.95947850745173502</v>
       </c>
       <c r="V27">
-        <f>B27/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.2396684904657094</v>
       </c>
       <c r="W27">
-        <f>C27/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.72923994073364662</v>
       </c>
       <c r="X27">
-        <f>D27/$D$31</f>
+        <f t="shared" si="19"/>
         <v>1.4991173772447719</v>
       </c>
       <c r="Z27">
-        <f>F27/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.74686753611341072</v>
       </c>
       <c r="AA27">
-        <f>G27/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.86438354357234937</v>
       </c>
       <c r="AB27">
-        <f>H27/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.73646382045603442</v>
       </c>
       <c r="AC27">
-        <f>I27/$D$31</f>
+        <f t="shared" si="7"/>
         <v>0.96713130962836502</v>
       </c>
       <c r="AE27">
-        <f>K27/$K$31</f>
+        <f t="shared" si="16"/>
         <v>1.0678076766626208</v>
       </c>
       <c r="AF27">
-        <f>L27/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.80390531793047382</v>
       </c>
       <c r="AG27">
-        <f>M27/$M$31</f>
+        <f t="shared" si="18"/>
         <v>1.0347561518413599</v>
       </c>
       <c r="AH27">
-        <f>N27/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.66873855040633978</v>
       </c>
       <c r="AJ27">
-        <f>P27/$K$31</f>
+        <f t="shared" si="21"/>
         <v>0.8913538938403498</v>
       </c>
       <c r="AK27">
-        <f>Q27/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.84631657684979078</v>
       </c>
       <c r="AL27">
-        <f>R27/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.44945905608488018</v>
       </c>
       <c r="AM27">
-        <f>S27/$N$31</f>
+        <f t="shared" si="14"/>
         <v>0.37340963093319918</v>
       </c>
     </row>
@@ -28496,59 +28496,59 @@
       </c>
       <c r="S28" s="7"/>
       <c r="U28">
-        <f>A28/$A$31</f>
+        <f t="shared" si="0"/>
         <v>0.94382183508475681</v>
       </c>
       <c r="V28">
-        <f>B28/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.1760081042920985</v>
       </c>
       <c r="W28">
-        <f>C28/$C$31</f>
+        <f t="shared" si="2"/>
         <v>0.73769500963806456</v>
       </c>
       <c r="X28">
-        <f>D28/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.95173701317513115</v>
       </c>
       <c r="Z28">
-        <f>F28/$A$31</f>
+        <f t="shared" si="4"/>
         <v>1.2179012483469587</v>
       </c>
       <c r="AA28">
-        <f>G28/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.98940008297348181</v>
       </c>
       <c r="AB28">
-        <f>H28/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.79408315982117172</v>
       </c>
       <c r="AE28">
-        <f>K28/$K$31</f>
+        <f t="shared" si="16"/>
         <v>0.95502452051193498</v>
       </c>
       <c r="AF28">
-        <f>L28/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.68670181067726321</v>
       </c>
       <c r="AG28">
-        <f>M28/$M$31</f>
+        <f t="shared" si="18"/>
         <v>0.44951017911632957</v>
       </c>
       <c r="AH28">
-        <f>N28/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.82520529024282585</v>
       </c>
       <c r="AJ28">
-        <f>P28/$K$31</f>
+        <f t="shared" si="21"/>
         <v>1.7812585821555764</v>
       </c>
       <c r="AK28">
-        <f>Q28/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.89555433362572834</v>
       </c>
       <c r="AL28">
-        <f>R28/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.44155617768681116</v>
       </c>
     </row>
@@ -28594,51 +28594,51 @@
       </c>
       <c r="S29" s="7"/>
       <c r="U29">
-        <f>A29/$A$31</f>
+        <f t="shared" si="0"/>
         <v>1.1105561256715697</v>
       </c>
       <c r="V29">
-        <f>B29/$B$31</f>
+        <f t="shared" si="1"/>
         <v>1.017694603266041</v>
       </c>
       <c r="W29">
-        <f>C29/$C$31</f>
+        <f t="shared" si="2"/>
         <v>1.7057375736259255</v>
       </c>
       <c r="X29">
-        <f>D29/$D$31</f>
+        <f t="shared" si="19"/>
         <v>0.75215911043965544</v>
       </c>
       <c r="Z29">
-        <f>F29/$A$31</f>
+        <f t="shared" si="4"/>
         <v>0.84960398205496612</v>
       </c>
       <c r="AA29">
-        <f>G29/$B$31</f>
+        <f t="shared" si="5"/>
         <v>0.87293537799249665</v>
       </c>
       <c r="AB29">
-        <f>H29/$C$31</f>
+        <f t="shared" si="15"/>
         <v>0.77509250014200581</v>
       </c>
       <c r="AF29">
-        <f>L29/$L$31</f>
+        <f t="shared" si="20"/>
         <v>0.53537885141490615</v>
       </c>
       <c r="AH29">
-        <f>N29/$N$31</f>
+        <f t="shared" si="9"/>
         <v>0.88140909271499601</v>
       </c>
       <c r="AJ29">
-        <f>P29/$K$31</f>
+        <f t="shared" si="21"/>
         <v>0.91734087112241158</v>
       </c>
       <c r="AK29">
-        <f>Q29/$L$31</f>
+        <f t="shared" si="11"/>
         <v>0.69873810891446908</v>
       </c>
       <c r="AL29">
-        <f>R29/$M$31</f>
+        <f t="shared" si="17"/>
         <v>0.58122058828644652</v>
       </c>
     </row>
@@ -28648,43 +28648,43 @@
         <v>1.1059725587999998</v>
       </c>
       <c r="B31">
-        <f t="shared" ref="B31:R31" si="0">AVERAGE(B5:B29)</f>
+        <f t="shared" ref="B31:R31" si="22">AVERAGE(B5:B29)</f>
         <v>1.1206028472</v>
       </c>
       <c r="C31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.4378700088</v>
       </c>
       <c r="D31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.6601479695833332</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.0906731664000002</v>
       </c>
       <c r="G31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.0230222212</v>
       </c>
       <c r="H31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.04290490625</v>
       </c>
       <c r="I31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>1.2308935699999999</v>
       </c>
       <c r="K31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.32282515619047614</v>
       </c>
       <c r="L31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.39732232499999992</v>
       </c>
       <c r="M31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.62242005409090895</v>
       </c>
       <c r="N31">
@@ -28692,15 +28692,15 @@
         <v>1.0153056819999997</v>
       </c>
       <c r="P31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.40151731875000002</v>
       </c>
       <c r="Q31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.28948638919999992</v>
       </c>
       <c r="R31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>0.28645280000000001</v>
       </c>
       <c r="S31">
@@ -28712,63 +28712,63 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="V31">
-        <f t="shared" ref="V31:AM31" si="1">AVERAGE(V5:V29)</f>
+        <f t="shared" ref="V31:AM31" si="23">AVERAGE(V5:V29)</f>
         <v>1</v>
       </c>
       <c r="W31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.99999999999999967</v>
       </c>
       <c r="X31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="Z31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.98616657142325492</v>
       </c>
       <c r="AA31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.91292131173517888</v>
       </c>
       <c r="AB31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.72531237167981188</v>
       </c>
       <c r="AC31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.74143606025005826</v>
       </c>
       <c r="AE31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="AF31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="AG31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="AH31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="AJ31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>1.2437609369980238</v>
       </c>
       <c r="AK31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.72859331325014276</v>
       </c>
       <c r="AL31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.46022424585657967</v>
       </c>
       <c r="AM31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>0.35093756083742145</v>
       </c>
     </row>
@@ -28936,67 +28936,67 @@
         <v>0.45003491000000001</v>
       </c>
       <c r="U35">
-        <f t="shared" ref="U35:U58" si="2">A35/$A$60</f>
+        <f t="shared" ref="U35:U58" si="24">A35/$A$60</f>
         <v>0.93908620527834252</v>
       </c>
       <c r="V35">
-        <f t="shared" ref="V35:V58" si="3">B35/$B$60</f>
+        <f t="shared" ref="V35:V58" si="25">B35/$B$60</f>
         <v>0.88629640961988254</v>
       </c>
       <c r="W35">
-        <f t="shared" ref="W35:W58" si="4">C35/$C$60</f>
+        <f t="shared" ref="W35:W58" si="26">C35/$C$60</f>
         <v>0.7650577302215541</v>
       </c>
       <c r="X35">
-        <f t="shared" ref="X35:X58" si="5">D35/$D$60</f>
+        <f t="shared" ref="X35:X58" si="27">D35/$D$60</f>
         <v>0.99599365228784753</v>
       </c>
       <c r="Z35">
-        <f t="shared" ref="Z35:Z58" si="6">F35/$A$60</f>
+        <f t="shared" ref="Z35:Z58" si="28">F35/$A$60</f>
         <v>0.99285490254685982</v>
       </c>
       <c r="AA35">
-        <f t="shared" ref="AA35:AA58" si="7">G35/$B$60</f>
+        <f t="shared" ref="AA35:AA58" si="29">G35/$B$60</f>
         <v>0.93814700865227874</v>
       </c>
       <c r="AB35">
-        <f t="shared" ref="AB35:AB58" si="8">H35/$C$60</f>
+        <f t="shared" ref="AB35:AB58" si="30">H35/$C$60</f>
         <v>1.1673398829512531</v>
       </c>
       <c r="AC35">
-        <f t="shared" ref="AC35:AC58" si="9">I35/$D$60</f>
+        <f t="shared" ref="AC35:AC58" si="31">I35/$D$60</f>
         <v>0.72379913444478072</v>
       </c>
       <c r="AE35">
-        <f t="shared" ref="AE35:AE58" si="10">K35/$K$60</f>
+        <f t="shared" ref="AE35:AE58" si="32">K35/$K$60</f>
         <v>0.7167092334005607</v>
       </c>
       <c r="AF35">
-        <f t="shared" ref="AF35:AF58" si="11">L35/$L$60</f>
+        <f t="shared" ref="AF35:AF58" si="33">L35/$L$60</f>
         <v>1.1208945661280205</v>
       </c>
       <c r="AG35">
-        <f t="shared" ref="AG35:AG58" si="12">M35/$M$60</f>
+        <f t="shared" ref="AG35:AG58" si="34">M35/$M$60</f>
         <v>1.3621073567566642</v>
       </c>
       <c r="AH35">
-        <f t="shared" ref="AH35:AH58" si="13">N35/$N$60</f>
+        <f t="shared" ref="AH35:AH58" si="35">N35/$N$60</f>
         <v>1.3401575633352685</v>
       </c>
       <c r="AJ35">
-        <f t="shared" ref="AJ35:AJ58" si="14">P35/$K$60</f>
+        <f t="shared" ref="AJ35:AJ58" si="36">P35/$K$60</f>
         <v>1.1553403279328724</v>
       </c>
       <c r="AK35">
-        <f t="shared" ref="AK35:AK58" si="15">Q35/$L$60</f>
+        <f t="shared" ref="AK35:AK58" si="37">Q35/$L$60</f>
         <v>0.72596146496153868</v>
       </c>
       <c r="AL35">
-        <f t="shared" ref="AL35:AL58" si="16">R35/$M$60</f>
+        <f t="shared" ref="AL35:AL58" si="38">R35/$M$60</f>
         <v>0.59540336492977886</v>
       </c>
       <c r="AM35">
-        <f t="shared" ref="AM35:AM58" si="17">S35/$N$60</f>
+        <f t="shared" ref="AM35:AM58" si="39">S35/$N$60</f>
         <v>0.3055592503510392</v>
       </c>
     </row>
@@ -29050,67 +29050,67 @@
         <v>0.58090346000000004</v>
       </c>
       <c r="U36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.99285226772684487</v>
       </c>
       <c r="V36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.0680039921446469</v>
       </c>
       <c r="W36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.84384031816754212</v>
       </c>
       <c r="X36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.1817225330427108</v>
       </c>
       <c r="Z36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.81612053999490219</v>
       </c>
       <c r="AA36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.83906885725099123</v>
       </c>
       <c r="AB36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.85505607929905958</v>
       </c>
       <c r="AC36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.99324152038533986</v>
       </c>
       <c r="AE36">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.66055984447983795</v>
       </c>
       <c r="AF36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.0253552012152092</v>
       </c>
       <c r="AG36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.29020490604471005</v>
       </c>
       <c r="AH36">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.1611187432350645</v>
       </c>
       <c r="AJ36">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.8284108271645253</v>
       </c>
       <c r="AK36">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.65221657340017991</v>
       </c>
       <c r="AL36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.30410714176291787</v>
       </c>
       <c r="AM36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.3944147927633545</v>
       </c>
     </row>
@@ -29162,63 +29162,63 @@
         <v>0.38484871999999998</v>
       </c>
       <c r="U37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.9307042140991737</v>
       </c>
       <c r="V37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.0317792375360595</v>
       </c>
       <c r="W37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.89256081460235392</v>
       </c>
       <c r="X37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.90823926738320016</v>
       </c>
       <c r="Z37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.8064573316442476</v>
       </c>
       <c r="AA37">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.90266006684748468</v>
       </c>
       <c r="AB37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.1860419551818602</v>
       </c>
       <c r="AC37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.66639477837864136</v>
       </c>
       <c r="AE37">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.74127477299286137</v>
       </c>
       <c r="AF37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.74496718672630891</v>
       </c>
       <c r="AG37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.6352880474422572</v>
       </c>
       <c r="AH37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.62397676732139018</v>
       </c>
       <c r="AJ37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.98023892768227872</v>
       </c>
       <c r="AK37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.77183892703140722</v>
       </c>
       <c r="AM37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.26129992089226362</v>
       </c>
     </row>
@@ -29270,63 +29270,63 @@
         <v>1.1774844499999999</v>
       </c>
       <c r="U38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.1728141145136772</v>
       </c>
       <c r="V38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.2454205824929074</v>
       </c>
       <c r="W38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.93584012759585744</v>
       </c>
       <c r="X38">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.9621949754577892</v>
       </c>
       <c r="Z38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.97685319010208793</v>
       </c>
       <c r="AA38">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.89744954150468192</v>
       </c>
       <c r="AB38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.5639600658335329</v>
       </c>
       <c r="AC38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.5785747254634932</v>
       </c>
       <c r="AE38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.7901676847064294</v>
       </c>
       <c r="AF38">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.91139934227620945</v>
       </c>
       <c r="AG38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.9173653364050327</v>
       </c>
       <c r="AH38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.5391213234567368</v>
       </c>
       <c r="AJ38">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.93658434435406634</v>
       </c>
       <c r="AK38">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.46286274050962295</v>
       </c>
       <c r="AM38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.79947412488956848</v>
       </c>
     </row>
@@ -29380,67 +29380,67 @@
         <v>0.96675032000000005</v>
       </c>
       <c r="U39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.88463723847253228</v>
       </c>
       <c r="V39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.1136757390656806</v>
       </c>
       <c r="W39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.91960006734612276</v>
       </c>
       <c r="X39">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.78382135037200085</v>
       </c>
       <c r="Z39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.0039945532585652</v>
       </c>
       <c r="AA39">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.87483418713664107</v>
       </c>
       <c r="AB39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.599210961386341</v>
       </c>
       <c r="AC39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.97479871850181743</v>
       </c>
       <c r="AE39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.1635087534461732</v>
       </c>
       <c r="AF39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.60064730320272186</v>
       </c>
       <c r="AG39">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.63741503834375557</v>
       </c>
       <c r="AH39">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.30145932315546403</v>
       </c>
       <c r="AJ39">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.97437094500789834</v>
       </c>
       <c r="AK39">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.6842771734593599</v>
       </c>
       <c r="AL39">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.30789036066856296</v>
       </c>
       <c r="AM39">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.65639241865887088</v>
       </c>
     </row>
@@ -29494,67 +29494,67 @@
         <v>0.55884849000000003</v>
       </c>
       <c r="U40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.1286286431050989</v>
       </c>
       <c r="V40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.78316315057315378</v>
       </c>
       <c r="W40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.79882277006573077</v>
       </c>
       <c r="X40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.7447971084791396</v>
       </c>
       <c r="Z40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.89312058290631946</v>
       </c>
       <c r="AA40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.91530596963150901</v>
       </c>
       <c r="AB40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.77823089785168365</v>
       </c>
       <c r="AC40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.78231279174832535</v>
       </c>
       <c r="AE40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.0927567137106424</v>
       </c>
       <c r="AF40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.62151938126926198</v>
       </c>
       <c r="AG40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.69676361819766597</v>
       </c>
       <c r="AH40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.2687392197899816</v>
       </c>
       <c r="AJ40">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.1216059304244932</v>
       </c>
       <c r="AK40">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.94058570037382605</v>
       </c>
       <c r="AL40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.40010018644370304</v>
       </c>
       <c r="AM40">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.3794401764614444</v>
       </c>
     </row>
@@ -29608,67 +29608,67 @@
         <v>0.64142228000000001</v>
       </c>
       <c r="U41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.94372811218878072</v>
       </c>
       <c r="V41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.90591761855734743</v>
       </c>
       <c r="W41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.84905040220593064</v>
       </c>
       <c r="X41">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.6750582690067237</v>
       </c>
       <c r="Z41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.95545549910333738</v>
       </c>
       <c r="AA41">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.75756748139598651</v>
       </c>
       <c r="AB41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.0868303854489547</v>
       </c>
       <c r="AC41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.88713281330504601</v>
       </c>
       <c r="AE41">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.88179015809238726</v>
       </c>
       <c r="AF41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.71132646943249633</v>
       </c>
       <c r="AG41">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.4137369024837273</v>
       </c>
       <c r="AH41">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>2.0294738272130739</v>
       </c>
       <c r="AJ41">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.0824046387692816</v>
       </c>
       <c r="AK41">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.47994896419565936</v>
       </c>
       <c r="AL41">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.29282414831313147</v>
       </c>
       <c r="AM41">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.43550512789164375</v>
       </c>
     </row>
@@ -29718,59 +29718,59 @@
         <v>0.56920064999999997</v>
       </c>
       <c r="U42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.83627569588188699</v>
       </c>
       <c r="V42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.3423433571325536</v>
       </c>
       <c r="W42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.95934234233155735</v>
       </c>
       <c r="Z42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.87334055100627761</v>
       </c>
       <c r="AA42">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.84614819329821978</v>
       </c>
       <c r="AB42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.78923353721855904</v>
       </c>
       <c r="AC42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.82197651703335861</v>
       </c>
       <c r="AE42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.99875172798844569</v>
       </c>
       <c r="AF42">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.2294065899822029</v>
       </c>
       <c r="AG42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.4188058324275512</v>
       </c>
       <c r="AJ42">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.64533101665038051</v>
       </c>
       <c r="AK42">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.77826725750425219</v>
       </c>
       <c r="AL42">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.4161915427689093</v>
       </c>
       <c r="AM42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.38646896062646396</v>
       </c>
     </row>
@@ -29824,67 +29824,67 @@
         <v>0.58394915999999997</v>
       </c>
       <c r="U43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.0058752063076803</v>
       </c>
       <c r="V43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.3153345259192164</v>
       </c>
       <c r="W43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.0100512196425941</v>
       </c>
       <c r="X43">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.14898671960407</v>
       </c>
       <c r="Z43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.0618767415197472</v>
       </c>
       <c r="AA43">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.84663475143966638</v>
       </c>
       <c r="AB43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.2946410676618092</v>
       </c>
       <c r="AC43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.0898442613557133</v>
       </c>
       <c r="AE43">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.78904290241779851</v>
       </c>
       <c r="AF43">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.4697645130952295</v>
       </c>
       <c r="AG43">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.1816120465344322</v>
       </c>
       <c r="AH43">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>2.1458749472867011</v>
       </c>
       <c r="AJ43">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.1312777864553651</v>
       </c>
       <c r="AK43">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.47937398759244026</v>
       </c>
       <c r="AL43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.55705263444366826</v>
       </c>
       <c r="AM43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.39648272524617933</v>
       </c>
     </row>
@@ -29936,63 +29936,63 @@
       </c>
       <c r="S44" s="8"/>
       <c r="U44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.8735351439693898</v>
       </c>
       <c r="V44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.83750742166488679</v>
       </c>
       <c r="W44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.98873332131695957</v>
       </c>
       <c r="X44">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.4088159498985102</v>
       </c>
       <c r="Z44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.0699178543662773</v>
       </c>
       <c r="AA44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.98105952961071641</v>
       </c>
       <c r="AB44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.99610464859581449</v>
       </c>
       <c r="AC44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.3177813917946486</v>
       </c>
       <c r="AE44">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.89444784060641536</v>
       </c>
       <c r="AF44">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.2826917001648015</v>
       </c>
       <c r="AG44">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.7425037882839354</v>
       </c>
       <c r="AH44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>2.2954305851280092</v>
       </c>
       <c r="AJ44">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.5610922344370535</v>
       </c>
       <c r="AK44">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.58256128100637117</v>
       </c>
       <c r="AL44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.56521446214938997</v>
       </c>
     </row>
@@ -30046,67 +30046,67 @@
         <v>1.0197845800000001</v>
       </c>
       <c r="U45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.88328345251842644</v>
       </c>
       <c r="V45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.2544842134258853</v>
       </c>
       <c r="W45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.2279155385359406</v>
       </c>
       <c r="X45">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.74917038355176824</v>
       </c>
       <c r="Z45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.9538379581327503</v>
       </c>
       <c r="AA45">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.84864074994757321</v>
       </c>
       <c r="AB45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.5258958965522516</v>
       </c>
       <c r="AC45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.254530623959232</v>
       </c>
       <c r="AE45">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.6837541003102926</v>
       </c>
       <c r="AF45">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.8121660225881111</v>
       </c>
       <c r="AG45">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.71562321934027884</v>
       </c>
       <c r="AH45">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.47200031701915768</v>
       </c>
       <c r="AJ45">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.233823598470055</v>
       </c>
       <c r="AK45">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.60772308231548111</v>
       </c>
       <c r="AL45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.49320902055700278</v>
       </c>
       <c r="AM45">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.69240097792491118</v>
       </c>
     </row>
@@ -30160,67 +30160,67 @@
         <v>0.79766775999999995</v>
       </c>
       <c r="U46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.0838405655070027</v>
       </c>
       <c r="V46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.72126673044520162</v>
       </c>
       <c r="W46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.9687648298904481</v>
       </c>
       <c r="X46">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.1459875020382784</v>
       </c>
       <c r="Z46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.92966386642826848</v>
       </c>
       <c r="AA46">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.9143102992060127</v>
       </c>
       <c r="AB46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.081293175332368</v>
       </c>
       <c r="AC46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.1003847534898459</v>
       </c>
       <c r="AE46">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.98751214050485758</v>
       </c>
       <c r="AF46">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.76458547718954017</v>
       </c>
       <c r="AG46">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.99948250986652798</v>
       </c>
       <c r="AH46">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.4477094301855562</v>
       </c>
       <c r="AJ46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.0120721162703492</v>
       </c>
       <c r="AK46">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.9119741216318803</v>
       </c>
       <c r="AL46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.46646635980180473</v>
       </c>
       <c r="AM46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.5415907907561941</v>
       </c>
     </row>
@@ -30272,63 +30272,63 @@
         <v>0.45954950999999999</v>
       </c>
       <c r="U47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.1853987656721945</v>
       </c>
       <c r="V47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.94996896726706859</v>
       </c>
       <c r="W47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.80664760784027234</v>
       </c>
       <c r="X47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.2171478195585805</v>
       </c>
       <c r="Z47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.1181417610258202</v>
       </c>
       <c r="AA47">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.81314642339987508</v>
       </c>
       <c r="AB47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.415163171052185</v>
       </c>
       <c r="AC47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.97833115446664587</v>
       </c>
       <c r="AE47">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.5764249936122573</v>
       </c>
       <c r="AF47">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.86373144777336108</v>
       </c>
       <c r="AG47">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.76397756758407942</v>
       </c>
       <c r="AH47">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.72340978064903128</v>
       </c>
       <c r="AJ47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.3646254340517365</v>
       </c>
       <c r="AK47">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.58921233683580909</v>
       </c>
       <c r="AM47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.31201935817554111</v>
       </c>
     </row>
@@ -30380,63 +30380,63 @@
         <v>0.85157753999999997</v>
       </c>
       <c r="U48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.93976925992015681</v>
       </c>
       <c r="V48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.0965051973051705</v>
       </c>
       <c r="W48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.78042565636577255</v>
       </c>
       <c r="X48">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.0941439380448812</v>
       </c>
       <c r="Z48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.97425741659031362</v>
       </c>
       <c r="AA48">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.75483558980534071</v>
       </c>
       <c r="AB48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.1647666650224944</v>
       </c>
       <c r="AC48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.307360479601078</v>
       </c>
       <c r="AE48">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.89268800453438835</v>
       </c>
       <c r="AF48">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.65888672936720893</v>
       </c>
       <c r="AG48">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.3072919403332266</v>
       </c>
       <c r="AH48">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.70305661841266609</v>
       </c>
       <c r="AJ48">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.1630150988042489</v>
       </c>
       <c r="AK48">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.54655464512019325</v>
       </c>
       <c r="AM48">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.57819379998361042</v>
       </c>
     </row>
@@ -30490,67 +30490,67 @@
         <v>0.37950890999999998</v>
       </c>
       <c r="U49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.8300327965647053</v>
       </c>
       <c r="V49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.2230202440319027</v>
       </c>
       <c r="W49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.6009491374016871</v>
       </c>
       <c r="X49">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.88493625895389749</v>
       </c>
       <c r="Z49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.95863907199778797</v>
       </c>
       <c r="AA49">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.78953314142140985</v>
       </c>
       <c r="AB49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.75166475694209256</v>
       </c>
       <c r="AC49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.0357067068329964</v>
       </c>
       <c r="AE49">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.65798879306865832</v>
       </c>
       <c r="AF49">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.73299809043596542</v>
       </c>
       <c r="AG49">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>2.5510423153246338</v>
       </c>
       <c r="AH49">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.5540522860843826</v>
       </c>
       <c r="AJ49">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.91755147883567978</v>
       </c>
       <c r="AK49">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.65326971093500685</v>
       </c>
       <c r="AL49">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.63675665338492793</v>
       </c>
       <c r="AM49">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.25767436139818578</v>
       </c>
     </row>
@@ -30604,67 +30604,67 @@
         <v>0.41849626000000001</v>
       </c>
       <c r="U50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.85351991816051442</v>
       </c>
       <c r="V50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.84247962677250721</v>
       </c>
       <c r="W50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.1811999000122662</v>
       </c>
       <c r="X50">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.003927293972543</v>
       </c>
       <c r="Z50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.1376442185735078</v>
       </c>
       <c r="AA50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.81066238620934472</v>
       </c>
       <c r="AB50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.81597579808979215</v>
       </c>
       <c r="AC50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.66799380126383112</v>
       </c>
       <c r="AE50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.99273119786004083</v>
       </c>
       <c r="AF50">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.90579389570017266</v>
       </c>
       <c r="AG50">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>1.7595001032469655</v>
       </c>
       <c r="AH50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.4825688906261763</v>
       </c>
       <c r="AJ50">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.4861159120180583</v>
       </c>
       <c r="AK50">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.50122101097821214</v>
       </c>
       <c r="AL50">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.39141000735482157</v>
       </c>
       <c r="AM50">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.28414551991158554</v>
       </c>
     </row>
@@ -30718,67 +30718,67 @@
         <v>0.50818808000000004</v>
       </c>
       <c r="U51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.79167762414123344</v>
       </c>
       <c r="V51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.84695708929067093</v>
       </c>
       <c r="W51">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.185116900725371</v>
       </c>
       <c r="X51">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.92081525602555492</v>
       </c>
       <c r="Z51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.77837043230767033</v>
       </c>
       <c r="AA51">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.98398007952317434</v>
       </c>
       <c r="AB51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.97368039693133712</v>
       </c>
       <c r="AC51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.89841531425305543</v>
       </c>
       <c r="AE51">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.0551588605991862</v>
       </c>
       <c r="AF51">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.9231278623068413</v>
       </c>
       <c r="AG51">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.91149145421117372</v>
       </c>
       <c r="AH51">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.77804434364934849</v>
       </c>
       <c r="AJ51">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.95980799221475166</v>
       </c>
       <c r="AK51">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.81526895795958598</v>
       </c>
       <c r="AL51">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.77130194996193568</v>
       </c>
       <c r="AM51">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.34504338510568872</v>
       </c>
     </row>
@@ -30832,67 +30832,67 @@
         <v>0.66692812999999995</v>
       </c>
       <c r="U52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.1512127860245362</v>
       </c>
       <c r="V52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.1300325847753843</v>
       </c>
       <c r="W52">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.0784724096491034</v>
       </c>
       <c r="X52">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.98804729616759501</v>
       </c>
       <c r="Z52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.0269939022200341</v>
       </c>
       <c r="AA52">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.82552091988327525</v>
       </c>
       <c r="AB52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.77670231490254416</v>
       </c>
       <c r="AC52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.73039966467182071</v>
       </c>
       <c r="AE52">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.3411418827032848</v>
       </c>
       <c r="AF52">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.1074223284587585</v>
       </c>
       <c r="AG52">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.38200851091164634</v>
       </c>
       <c r="AH52">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.51848750305604141</v>
       </c>
       <c r="AJ52">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.88934721998646638</v>
       </c>
       <c r="AK52">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.61441381777671344</v>
       </c>
       <c r="AL52">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.29677869296405579</v>
       </c>
       <c r="AM52">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.4528227808834217</v>
       </c>
     </row>
@@ -30946,67 +30946,67 @@
         <v>0.52072618999999998</v>
       </c>
       <c r="U53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.1492225567462853</v>
       </c>
       <c r="V53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.76975411940589566</v>
       </c>
       <c r="W53">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.046464554818741</v>
       </c>
       <c r="X53">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.96917433231267602</v>
       </c>
       <c r="Z53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.98173246123160385</v>
       </c>
       <c r="AA53">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.93711887372488045</v>
       </c>
       <c r="AB53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.1971137149412499</v>
       </c>
       <c r="AC53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.84931592646777554</v>
       </c>
       <c r="AE53">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.3373835529080134</v>
       </c>
       <c r="AF53">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.1636696858840423</v>
       </c>
       <c r="AG53">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.89823715788069736</v>
       </c>
       <c r="AH53">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.5544768950587301</v>
       </c>
       <c r="AJ53">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.78464215017263805</v>
       </c>
       <c r="AK53">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.94148904483303453</v>
       </c>
       <c r="AL53">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.91810083571589662</v>
       </c>
       <c r="AM53">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.35355635911568017</v>
       </c>
     </row>
@@ -31060,67 +31060,67 @@
         <v>1.25083955</v>
       </c>
       <c r="U54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>0.98993428594936383</v>
       </c>
       <c r="V54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.86432410125318326</v>
       </c>
       <c r="W54">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.95074079519546884</v>
       </c>
       <c r="X54">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.7294520758353642</v>
       </c>
       <c r="Z54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.95060035150487432</v>
       </c>
       <c r="AA54">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.9414985314977582</v>
       </c>
       <c r="AB54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.95377184161284323</v>
       </c>
       <c r="AC54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.5085162043944145</v>
       </c>
       <c r="AE54">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.90516515612791038</v>
       </c>
       <c r="AF54">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>1.3508168447028737</v>
       </c>
       <c r="AG54">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.822449998359157</v>
       </c>
       <c r="AH54">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.37000290989226475</v>
       </c>
       <c r="AJ54">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.93449250980638321</v>
       </c>
       <c r="AK54">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.80536857751824587</v>
       </c>
       <c r="AL54">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.79276260552007183</v>
       </c>
       <c r="AM54">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.84927988188167725</v>
       </c>
     </row>
@@ -31174,67 +31174,67 @@
         <v>0.64094662000000002</v>
       </c>
       <c r="U55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.266047281327616</v>
       </c>
       <c r="V55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.85144692638551123</v>
       </c>
       <c r="W55">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.0415913687070721</v>
       </c>
       <c r="X55">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.86516517575973462</v>
       </c>
       <c r="Z55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.91613923692877952</v>
       </c>
       <c r="AA55">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>1.0349394292803198</v>
       </c>
       <c r="AB55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.88278820729753615</v>
       </c>
       <c r="AC55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.99087618466600669</v>
       </c>
       <c r="AE55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.6774273221296498</v>
       </c>
       <c r="AF55">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.91904059723527909</v>
       </c>
       <c r="AG55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.85622330958241633</v>
       </c>
       <c r="AH55">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.37232306536445819</v>
       </c>
       <c r="AJ55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.1357708700542772</v>
       </c>
       <c r="AK55">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.61039302512891958</v>
       </c>
       <c r="AL55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.31439894700703491</v>
       </c>
       <c r="AM55">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.4351821700281705</v>
       </c>
     </row>
@@ -31288,67 +31288,67 @@
         <v>0.50313072999999997</v>
       </c>
       <c r="U56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.0337662072765255</v>
       </c>
       <c r="V56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.032327326073877</v>
       </c>
       <c r="W56">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.87271592286029831</v>
       </c>
       <c r="X56">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.72890240300170617</v>
       </c>
       <c r="Z56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>1.1450736015226051</v>
       </c>
       <c r="AA56">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>1.0650420744532398</v>
       </c>
       <c r="AB56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.3659591663306561</v>
       </c>
       <c r="AC56">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.6737189583369193</v>
       </c>
       <c r="AE56">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.99523442692670261</v>
       </c>
       <c r="AF56">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.86157203092674306</v>
       </c>
       <c r="AG56">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.60734334191646422</v>
       </c>
       <c r="AH56">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.0801301301018964</v>
       </c>
       <c r="AJ56">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>0.99373526905250376</v>
       </c>
       <c r="AK56">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.74057075256012272</v>
       </c>
       <c r="AL56">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.5581457358899139</v>
       </c>
       <c r="AM56">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.3416096068799887</v>
       </c>
     </row>
@@ -31402,67 +31402,67 @@
         <v>0.42606997000000002</v>
       </c>
       <c r="U57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.0643866407690858</v>
       </c>
       <c r="V57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>1.0547080355505019</v>
       </c>
       <c r="W57">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>0.92153625486854263</v>
       </c>
       <c r="X57">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>0.96370057905174933</v>
       </c>
       <c r="Z57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.82125196210701668</v>
       </c>
       <c r="AA57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.9730129843733718</v>
       </c>
       <c r="AB57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>1.1846022919455477</v>
       </c>
       <c r="AC57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>0.80904766014646168</v>
       </c>
       <c r="AE57">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>0.87125126064577463</v>
       </c>
       <c r="AF57">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.95753056331693254</v>
       </c>
       <c r="AG57">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.47609672452780738</v>
       </c>
       <c r="AH57">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>0.68136700295310337</v>
       </c>
       <c r="AJ57">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.2256552199088788</v>
       </c>
       <c r="AK57">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.79602663776066107</v>
       </c>
       <c r="AL57">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.58183603842032738</v>
       </c>
       <c r="AM57">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.28928782576064993</v>
       </c>
     </row>
@@ -31516,67 +31516,67 @@
         <v>0.63192409999999999</v>
       </c>
       <c r="U58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>1.073662397028351</v>
       </c>
       <c r="V58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="25"/>
         <v>0.90588459296647628</v>
       </c>
       <c r="W58">
-        <f t="shared" si="4"/>
+        <f t="shared" si="26"/>
         <v>1.0552055122268038</v>
       </c>
       <c r="X58">
-        <f t="shared" si="5"/>
+        <f t="shared" si="27"/>
         <v>1.0427740547272533</v>
       </c>
       <c r="Z58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="28"/>
         <v>0.91916355546421646</v>
       </c>
       <c r="AA58">
-        <f t="shared" si="7"/>
+        <f t="shared" si="29"/>
         <v>0.99726904796824078</v>
       </c>
       <c r="AB58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="30"/>
         <v>0.77894991291060767</v>
       </c>
       <c r="AC58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="31"/>
         <v>1.091165804974545</v>
       </c>
       <c r="AE58">
-        <f t="shared" si="10"/>
+        <f t="shared" si="32"/>
         <v>1.3565809386722913</v>
       </c>
       <c r="AF58">
-        <f t="shared" si="11"/>
+        <f t="shared" si="33"/>
         <v>0.73462013921190195</v>
       </c>
       <c r="AG58">
-        <f t="shared" si="12"/>
+        <f t="shared" si="34"/>
         <v>0.79593603740983332</v>
       </c>
       <c r="AH58">
-        <f t="shared" si="13"/>
+        <f t="shared" si="35"/>
         <v>1.0617460833625889</v>
       </c>
       <c r="AJ58">
-        <f t="shared" si="14"/>
+        <f t="shared" si="36"/>
         <v>1.1692210898262814</v>
       </c>
       <c r="AK58">
-        <f t="shared" si="15"/>
+        <f t="shared" si="37"/>
         <v>0.89725235361889288</v>
       </c>
       <c r="AL58">
-        <f t="shared" si="16"/>
+        <f t="shared" si="38"/>
         <v>0.20214479781268932</v>
       </c>
       <c r="AM58">
-        <f t="shared" si="17"/>
+        <f t="shared" si="39"/>
         <v>0.42905616871978919</v>
       </c>
     </row>
@@ -31586,63 +31586,63 @@
         <v>0.86502596399999987</v>
       </c>
       <c r="B60">
-        <f t="shared" ref="B60:S60" si="18">AVERAGE(B34:B58)</f>
+        <f t="shared" ref="B60:S60" si="40">AVERAGE(B34:B58)</f>
         <v>0.99801393799999982</v>
       </c>
       <c r="C60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.1403750795999998</v>
       </c>
       <c r="D60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.3244787724999998</v>
       </c>
       <c r="F60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.83248136267105255</v>
       </c>
       <c r="G60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.89670306621495754</v>
       </c>
       <c r="H60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.1937151361566487</v>
       </c>
       <c r="I60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.3050113843329856</v>
       </c>
       <c r="K60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.42596581119999999</v>
       </c>
       <c r="L60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.6083725807999999</v>
       </c>
       <c r="M60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.3058165872</v>
       </c>
       <c r="N60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>1.4728237141666669</v>
       </c>
       <c r="P60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.4575911467999999</v>
       </c>
       <c r="Q60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.42743631440000002</v>
       </c>
       <c r="R60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.63541406047619053</v>
       </c>
       <c r="S60">
-        <f t="shared" si="18"/>
+        <f t="shared" si="40"/>
         <v>0.65760173791666665</v>
       </c>
       <c r="U60">
@@ -31650,68 +31650,70 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="V60">
-        <f t="shared" ref="V60:AM60" si="19">AVERAGE(V34:V58)</f>
+        <f t="shared" ref="V60:AM60" si="41">AVERAGE(V34:V58)</f>
         <v>1</v>
       </c>
       <c r="W60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="X60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="Z60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.96237731272428362</v>
       </c>
       <c r="AA60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.89848751813219441</v>
       </c>
       <c r="AB60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>1.0467741338010987</v>
       </c>
       <c r="AC60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.98530184962476297</v>
       </c>
       <c r="AE60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>1</v>
       </c>
       <c r="AF60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>1.0000000000000002</v>
       </c>
       <c r="AG60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="AH60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.99999999999999967</v>
       </c>
       <c r="AJ60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>1.0742438354639481</v>
       </c>
       <c r="AK60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.7025897088227222</v>
       </c>
       <c r="AL60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.48660284047905866</v>
       </c>
       <c r="AM60">
-        <f t="shared" si="19"/>
+        <f t="shared" si="41"/>
         <v>0.44649046018976007</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="Z3:AC3"/>
+    <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AJ3:AM3"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="U2:X2"/>
@@ -31728,8 +31730,6 @@
     <mergeCell ref="K3:N3"/>
     <mergeCell ref="P3:S3"/>
     <mergeCell ref="U3:X3"/>
-    <mergeCell ref="Z3:AC3"/>
-    <mergeCell ref="AE3:AH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
